--- a/Re02_0005_rename.xlsx
+++ b/Re02_0005_rename.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LinhLT\File test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\リンLinhLT\Documents\Local_copy\8352\8352_Project033 1\branches02\5.2.1_8352_repoGithub001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6605F35C-5C74-4593-94E8-5495620EDF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593DCA34-4F35-4F57-B586-12FA4CFD4556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -348,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -361,6 +361,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1212121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
